--- a/stories/arbres/ATOM-REL.MOQ.004-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Armand est au parc avec papa. Flore fait une grimace drôle. Armand veut une photo. Papa a le téléphone. Papa, c'est l'adulte. Armand va demander. Il dit : on peut ? Pas pour rire de l'autre. Papa dit : on demande. Le téléphone photographie avec un adulte. Flore dit oui. Papa prend la photo. Armand dit merci. Ce n'est pas pour rire de Flore. Ils regardent le canard. Armand donne la main à papa. Le téléphone reste avec l'adulte.</t>
+          <t>Armand est au parc avec papa. Flore fait une grimace drôle. Armand veut une photo. Papa a le téléphone. Papa, c'est l'adulte. Armand va demander. On peut ? Pas pour rire de l'autre. On demande. Le téléphone photographie avec un adulte. Flore dit oui. Papa prend la photo. Armand dit merci. Ce n'est pas pour rire de Flore. Ils regardent le canard. Armand donne la main à papa. Le téléphone reste avec l'adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Armand est au parc avec papa. Flore fait une grimace drôle. Armand veut une photo. Papa a le téléphone. Papa, c'est l'adulte. Armand va demander.
+narrateur|On peut ? Pas pour rire de l'autre.
+papa|On demande.
+narrateur|Le téléphone photographie avec un adulte. Flore dit oui. Papa prend la photo. Armand dit merci. Ce n'est pas pour rire de Flore. Ils regardent le canard. Armand donne la main à papa. Le téléphone reste avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Armand veut une photo. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Armand a demandé à papa. Pas pour rire de l'autre. L'adulte a le téléphone.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le téléphone. Armand donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,11 @@
 narrateur|Le téléphone photographie avec un adulte. Flore dit oui. Papa prend la photo. Armand dit merci. Ce n'est pas pour rire de Flore. Ils regardent le canard. Armand donne la main à papa. Le téléphone reste avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1506,7 @@
           <t>narrateur|Armand veut une photo. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1678,7 @@
           <t>narrateur|Armand a demandé à papa. Pas pour rire de l'autre. L'adulte a le téléphone.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1846,7 @@
           <t>narrateur|Papa range le téléphone. Armand donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.004-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Armand demande avant la photo</t>
+          <t>Victorino demande avant la photo</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Au parc, près du bassin, Victorino veut une photo de la grimace de Sarah. Il demande. Le téléphone reste avec papa. Ce n'est pas pour rire. Puis ils demandent pour le canard.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Armand est au parc avec papa. Flore fait une grimace drôle. Armand veut une photo. Papa a le téléphone. Papa, c'est l'adulte. Armand va demander. On peut ? Pas pour rire de l'autre. On demande. Le téléphone photographie avec un adulte. Flore dit oui. Papa prend la photo. Armand dit merci. Ce n'est pas pour rire de Flore. Ils regardent le canard. Armand donne la main à papa. Le téléphone reste avec l'adulte.</t>
+          <t>Le bassin du parc est calme, tout lisse. Un canard laisse un V sur l'eau. Des miettes sèchent sur le banc chaud. Le vent sent l'herbe coupée. Une feuille tourne, puis s'arrête. Le bois du banc est un peu rugueux. Tu as vu le canard, Victorino ? Il fait un trait sur l'eau. Oui. C'est le trait sur l'eau. En ce moment, Victorino est près du banc. Sarah est là aussi. Sarah fait une grimace drôle. Son nez se plisse. Victorino rit avec elle. Encore, Sarah ! Sarah recommence. Victorino voit le téléphone de papa. Le téléphone est dans la main de papa. On peut une photo ? On demande. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Victorino se tourne vers Sarah. Sarah, on peut ? Sarah dit oui. Bravo, Victorino. Tu as demandé. Tu as fait du bon travail. Papa lève le téléphone. Le téléphone reste dans sa main. Papa prend la photo. Victorino et Sarah sourient. Merci, papa. De rien. Le canard s'approche un peu. Il fait coin, tout doux. Et le canard ? On peut une photo du canard ? On demande encore. Le téléphone reste avec moi. On peut, papa ? Oui. Papa photographie le canard. Sarah reste près du banc. Ce n'est pas pour rire de l'autre. C'est pour garder le bassin. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils regardent le canard. L'eau tremble, toute brillante. Tu donnes la main ? Oui, papa. Victorino donne la main à papa. Le téléphone reste avec l'adulte. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. Une miette tombe du banc. Le canard nage vers le milieu. Le parc sent l'herbe et l'eau. Victorino pose la main sur le bois du banc. Le bois est chaud et rugueux. Tu as chaud, toi ? Un peu. On reste à l'ombre. Sarah suit le canard des yeux. L'eau fait un petit clapotis. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Une feuille tourne encore, puis s'arrête. Le canard est loin. Oui. On le regarde d'ici. Le vent sent toujours l'herbe coupée.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,10 +1324,91 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Armand est au parc avec papa. Flore fait une grimace drôle. Armand veut une photo. Papa a le téléphone. Papa, c'est l'adulte. Armand va demander.
-narrateur|On peut ? Pas pour rire de l'autre.
+          <t>narrateur|Le bassin du parc est calme, tout lisse.
+narrateur|Un canard laisse un V sur l'eau.
+narrateur|Des miettes sèchent sur le banc chaud.
+narrateur|Le vent sent l'herbe coupée.
+narrateur|Une feuille tourne, puis s'arrête.
+narrateur|Le bois du banc est un peu rugueux.
+papa|Tu as vu le canard, Victorino ?
+enfant-m|Il fait un trait sur l'eau.
+papa|Oui.
+papa|C'est le trait sur l'eau.
+narrateur|En ce moment, Victorino est près du banc.
+narrateur|Sarah est là aussi.
+narrateur|Sarah fait une grimace drôle.
+narrateur|Son nez se plisse.
+narrateur|Victorino rit avec elle.
+enfant-m|Encore, Sarah !
+narrateur|Sarah recommence.
+narrateur|Victorino voit le téléphone de papa.
+narrateur|Le téléphone est dans la main de papa.
+enfant-m|On peut une photo ?
 papa|On demande.
-narrateur|Le téléphone photographie avec un adulte. Flore dit oui. Papa prend la photo. Armand dit merci. Ce n'est pas pour rire de Flore. Ils regardent le canard. Armand donne la main à papa. Le téléphone reste avec l'adulte.</t>
+papa|Demander, c'est parler avant.
+papa|Une photo se fait avec un adulte.
+papa|Le téléphone reste avec l'adulte.
+papa|Ce n'est pas pour rire de l'autre.
+enfant-m|D'accord.
+narrateur|Victorino se tourne vers Sarah.
+enfant-m|Sarah, on peut ?
+narrateur|Sarah dit oui.
+papa|Bravo, Victorino.
+papa|Tu as demandé.
+papa|Tu as fait du bon travail.
+narrateur|Papa lève le téléphone.
+narrateur|Le téléphone reste dans sa main.
+narrateur|Papa prend la photo.
+narrateur|Victorino et Sarah sourient.
+enfant-m|Merci, papa.
+papa|De rien.
+narrateur|Le canard s'approche un peu.
+narrateur|Il fait coin, tout doux.
+enfant-m|Et le canard ?
+enfant-m|On peut une photo du canard ?
+papa|On demande encore.
+papa|Le téléphone reste avec moi.
+enfant-m|On peut, papa ?
+papa|Oui.
+narrateur|Papa photographie le canard.
+narrateur|Sarah reste près du banc.
+narrateur|Ce n'est pas pour rire de l'autre.
+narrateur|C'est pour garder le bassin.
+papa|Tu as demandé deux fois.
+papa|Bravo.
+enfant-m|Le téléphone est avec toi.
+papa|Oui.
+papa|Avec l'adulte.
+narrateur|Ils regardent le canard.
+narrateur|L'eau tremble, toute brillante.
+papa|Tu donnes la main ?
+enfant-m|Oui, papa.
+narrateur|Victorino donne la main à papa.
+narrateur|Le téléphone reste avec l'adulte.
+papa|Vous avez demandé avant la photo.
+papa|C'est le bon geste.
+enfant-m|On demande.
+enfant-m|L'adulte a le téléphone.
+papa|Oui.
+papa|Pas pour rire de l'autre.
+narrateur|Une miette tombe du banc.
+narrateur|Le canard nage vers le milieu.
+narrateur|Le parc sent l'herbe et l'eau.
+narrateur|Victorino pose la main sur le bois du banc.
+narrateur|Le bois est chaud et rugueux.
+papa|Tu as chaud, toi ?
+enfant-m|Un peu.
+papa|On reste à l'ombre.
+narrateur|Sarah suit le canard des yeux.
+narrateur|L'eau fait un petit clapotis.
+papa|On a demandé avant la photo.
+enfant-m|Et le téléphone est avec toi.
+papa|Oui.
+narrateur|Une feuille tourne encore, puis s'arrête.
+enfant-m|Le canard est loin.
+papa|Oui.
+papa|On le regarde d'ici.
+narrateur|Le vent sent toujours l'herbe coupée.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1347,7 +1440,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Armand veut une photo. Que fait-il ?</t>
+          <t>Victorino veut une photo. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,7 +1596,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Armand veut une photo. Que fait-il ?</t>
+          <t>narrateur|Victorino veut une photo.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1625,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Armand a demandé à papa. Pas pour rire de l'autre. L'adulte a le téléphone.</t>
+          <t>Victorino a demandé à papa. Pas pour rire de l'autre. L'adulte a le téléphone. Bravo, Victorino. Tu as fait du bon travail. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,7 +1769,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Armand a demandé à papa. Pas pour rire de l'autre. L'adulte a le téléphone.</t>
+          <t>narrateur|Victorino a demandé à papa.
+narrateur|Pas pour rire de l'autre.
+narrateur|L'adulte a le téléphone.
+papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+enfant-m|J'ai demandé.
+enfant-m|Le téléphone est avec toi.
+papa|Oui.
+papa|Avec l'adulte.
+papa|On demande avant une photo.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1806,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le téléphone. Armand donne la main.</t>
+          <t>Papa range le téléphone. Victorino donne la main. On reste un peu sur le banc ? Oui, papa. Sarah s'assoit à côté. Le canard nage, loin maintenant. Tu as demandé. C'était le bon geste. Pas pour rire de l'autre. Oui. Le banc est encore chaud. L'eau du bassin est calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1946,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le téléphone. Armand donne la main.</t>
+          <t>narrateur|Papa range le téléphone.
+narrateur|Victorino donne la main.
+papa|On reste un peu sur le banc ?
+enfant-m|Oui, papa.
+narrateur|Sarah s'assoit à côté.
+narrateur|Le canard nage, loin maintenant.
+papa|Tu as demandé.
+papa|C'était le bon geste.
+enfant-m|Pas pour rire de l'autre.
+papa|Oui.
+narrateur|Le banc est encore chaud.
+narrateur|L'eau du bassin est calme.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1985,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a demandé. Le téléphone est avec papa. Bravo. Tu as fait du bon travail. Le canard laisse encore un V. Le parc sent l'herbe coupée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2125,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a demandé.
+enfant-m|Le téléphone est avec papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le canard laisse encore un V.
+narrateur|Le parc sent l'herbe coupée.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2191,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le bassin du parc est calme, tout lisse. Un canard laisse un V sur l'eau. Des miettes sèchent sur le banc chaud. Le vent sent l'herbe coupée. Une feuille tourne, puis s'arrête. Le bois du banc est un peu rugueux. Tu as vu le canard, Victorino ? Il fait un trait sur l'eau. Oui. C'est le trait sur l'eau. En ce moment, Victorino est près du banc. Sarah est là aussi. Sarah fait une grimace drôle. Son nez se plisse. Victorino rit avec elle. Encore, Sarah ! Sarah recommence. Victorino voit le téléphone de papa. Le téléphone est dans la main de papa. On peut une photo ? On demande. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Victorino se tourne vers Sarah. Sarah, on peut ? Sarah dit oui. Bravo, Victorino. Tu as demandé. Tu as fait du bon travail. Papa lève le téléphone. Le téléphone reste dans sa main. Papa prend la photo. Victorino et Sarah sourient. Merci, papa. De rien. Le canard s'approche un peu. Il fait coin, tout doux. Et le canard ? On peut une photo du canard ? On demande encore. Le téléphone reste avec moi. On peut, papa ? Oui. Papa photographie le canard. Sarah reste près du banc. Ce n'est pas pour rire de l'autre. C'est pour garder le bassin. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils regardent le canard. L'eau tremble, toute brillante. Tu donnes la main ? Oui, papa. Victorino donne la main à papa. Le téléphone reste avec l'adulte. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. Une miette tombe du banc. Le canard nage vers le milieu. Le parc sent l'herbe et l'eau. Victorino pose la main sur le bois du banc. Le bois est chaud et rugueux. Tu as chaud, toi ? Un peu. On reste à l'ombre. Sarah suit le canard des yeux. L'eau fait un petit clapotis. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Une feuille tourne encore, puis s'arrête. Le canard est loin. Oui. On le regarde d'ici. Le vent sent toujours l'herbe coupée.</t>
+          <t>Le bassin du parc est calme, tout lisse. Un canard laisse un V sur l'eau. Des miettes sèchent sur le banc chaud. Le vent sent l'herbe coupée. Une feuille tourne, puis s'arrête. Le bois du banc est un peu rugueux. Tu as vu le canard, Victorino ? Il fait un trait sur l'eau. Oui. C'est le trait sur l'eau. En ce moment, Victorino est près du banc. Sarah est là aussi. Sarah fait une grimace drôle. Son nez se plisse. Victorino rit avec elle. Encore, Sarah ! Sarah recommence. Victorino voit le téléphone de papa. Le téléphone est dans la main de papa. On peut une photo ? On demande. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Victorino se tourne vers Sarah. Sarah, on peut ? Sarah dit oui. Bravo, Victorino. Tu as demandé. Papa lève le téléphone. Le téléphone reste dans sa main. Papa prend la photo. Victorino et Sarah sourient. Merci, papa. De rien. Le canard s'approche un peu. Il fait coin, tout doux. Et le canard ? On peut une photo du canard ? On demande encore. Le téléphone reste avec moi. On peut, papa ? Oui. Papa photographie le canard. Sarah reste près du banc. Ce n'est pas pour rire de l'autre. C'est pour garder le bassin. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils regardent le canard. L'eau tremble, toute brillante. Tu donnes la main ? Oui, papa. Victorino donne la main à papa. Le téléphone reste avec l'adulte. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. Une miette tombe du banc. Le canard nage vers le milieu. Le parc sent l'herbe et l'eau. Victorino pose la main sur le bois du banc. Le bois est chaud et rugueux. Tu as chaud, toi ? Un peu. On reste à l'ombre. Sarah suit le canard des yeux. L'eau fait un petit clapotis. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Une feuille tourne encore, puis s'arrête. Le canard est loin. Oui. On le regarde d'ici. Le vent sent toujours l'herbe coupée.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Armand est au parc avec papa. Flore fait une grimace drôle. Armand veut une photo. Papa a le téléphone. Papa, c'est l'adulte. Armand va &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt;. Il dit : on peut ? Pas pour rire de l'autre. Papa dit : on demande. Le téléphone photographie avec un adulte. Flore dit oui. Papa prend la photo. Armand dit merci. Ce n'est pas pour rire de Flore. Ils regardent le canard. Armand donne la main à papa. Le téléphone reste avec l'adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bassin du parc est calme, tout lisse. Un canard laisse un V sur l'eau. Des miettes sèchent sur le banc chaud. Le vent sent l'herbe coupée. Une feuille tourne, puis s'arrête. Le bois du banc est un peu rugueux. Tu as vu le canard, Victorino ? Il fait un trait sur l'eau. Oui. C'est le trait sur l'eau. En ce moment, Victorino est près du banc. Sarah est là aussi. Sarah fait une grimace drôle. Son nez se plisse. Victorino rit avec elle. Encore, Sarah ! Sarah recommence. Victorino voit le téléphone de papa. Le téléphone est dans la main de papa. On peut une photo ? On demande. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Victorino se tourne vers Sarah. Sarah, on peut ? Sarah dit oui. Bravo, Victorino. Tu as demandé. Papa lève le téléphone. Le téléphone reste dans sa main. Papa prend la photo. Victorino et Sarah sourient. Merci, papa. De rien. Le canard s'approche un peu. Il fait coin, tout doux. Et le canard ? On peut une photo du canard ? On demande encore. Le téléphone reste avec moi. On peut, papa ? Oui. Papa photographie le canard. Sarah reste près du banc. Ce n'est pas pour rire de l'autre. C'est pour garder le bassin. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils regardent le canard. L'eau tremble, toute brillante. Tu donnes la main ? Oui, papa. Victorino donne la main à papa. Le téléphone reste avec l'adulte. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. Une miette tombe du banc. Le canard nage vers le milieu. Le parc sent l'herbe et l'eau. Victorino pose la main sur le bois du banc. Le bois est chaud et rugueux. Tu as chaud, toi ? Un peu. On reste à l'ombre. Sarah suit le canard des yeux. L'eau fait un petit clapotis. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Une feuille tourne encore, puis s'arrête. Le canard est loin. Oui. On le regarde d'ici. Le vent sent toujours l'herbe coupée.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1355,7 +1355,6 @@
 narrateur|Sarah dit oui.
 papa|Bravo, Victorino.
 papa|Tu as demandé.
-papa|Tu as fait du bon travail.
 narrateur|Papa lève le téléphone.
 narrateur|Le téléphone reste dans sa main.
 narrateur|Papa prend la photo.
@@ -1445,7 +1444,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Armand veut une photo. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino veut une photo. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1600,7 +1599,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1625,12 +1623,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a demandé à papa. Pas pour rire de l'autre. L'adulte a le téléphone. Bravo, Victorino. Tu as fait du bon travail. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
+          <t>Victorino a demandé à papa. Pas pour rire de l'autre. L'adulte a le téléphone. Bravo, Victorino. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Armand a demandé à papa. Pas pour rire de l'autre. L'&lt;emphasis level="moderate"&gt;adulte&lt;/emphasis&gt; a le téléphone.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a demandé à papa. Pas pour rire de l'autre. L'adulte a le téléphone. Bravo, Victorino. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1773,7 +1771,6 @@
 narrateur|Pas pour rire de l'autre.
 narrateur|L'adulte a le téléphone.
 papa|Bravo, Victorino.
-papa|Tu as fait du bon travail.
 enfant-m|J'ai demandé.
 enfant-m|Le téléphone est avec toi.
 papa|Oui.
@@ -1781,7 +1778,6 @@
 papa|On demande avant une photo.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1811,7 +1807,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range le téléphone. Armand donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa range le téléphone. Victorino donne la main. On reste un peu sur le banc ? Oui, papa. Sarah s'assoit à côté. Le canard nage, loin maintenant. Tu as demandé. C'était le bon geste. Pas pour rire de l'autre. Oui. Le banc est encore chaud. L'eau du bassin est calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1960,7 +1956,6 @@
 narrateur|L'eau du bassin est calme.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1985,12 +1980,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a demandé. Le téléphone est avec papa. Bravo. Tu as fait du bon travail. Le canard laisse encore un V. Le parc sent l'herbe coupée. L'histoire est finie.</t>
+          <t>On a demandé. Le téléphone est avec papa. Bravo. Le canard laisse encore un V. Le parc sent l'herbe coupée.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a demandé. Le téléphone est avec papa. Bravo. Le canard laisse encore un V. Le parc sent l'herbe coupée.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2128,13 +2123,10 @@
           <t>enfant-m|On a demandé.
 enfant-m|Le téléphone est avec papa.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Le canard laisse encore un V.
-narrateur|Le parc sent l'herbe coupée.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le parc sent l'herbe coupée.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2153,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2198,6 +2190,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Armand, Flore, papa</t>
+          <t>Victorino, Sarah, papa</t>
         </is>
       </c>
     </row>
